--- a/scripts/cards.xlsx
+++ b/scripts/cards.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="833">
   <si>
     <t>id</t>
   </si>
@@ -1702,91 +1702,91 @@
     <t>Alongside the sharpnose sevengill (Heptranchias perlo), it's listed in the Guinness World Records as the fish with the most gill slits.</t>
   </si>
   <si>
+    <t>Common Bluestripe Snapper</t>
+  </si>
+  <si>
+    <t>Lutjanus kasmira</t>
+  </si>
+  <si>
+    <t>[BlueCoral][BlueCoral][BlueCoral]</t>
+  </si>
+  <si>
+    <t>It has a varied diet, feeding on fishes, shrimps, crabs, and crustaceans, as well as plant and algae material.</t>
+  </si>
+  <si>
+    <t>Daggertooth</t>
+  </si>
+  <si>
+    <t>Anotopterus pharao</t>
+  </si>
+  <si>
+    <t>[FishHatch] also, if [GreenCoral][GreenCoral][GreenCoral] in this dive site: [Discard]</t>
+  </si>
+  <si>
+    <t>Older daggertooth appear to turn black, lose their teeth, and migrate to deeper waters, possibly to reproduce.</t>
+  </si>
+  <si>
+    <t>Dusky Shark</t>
+  </si>
+  <si>
+    <t>Carcharhinus obscurus</t>
+  </si>
+  <si>
+    <t>[FreePlayFishFromHand][FishLengthMedium]only</t>
+  </si>
+  <si>
+    <t>It migrates hundreds to thousands of km to temperate waters in the summer and toward the equator in the winter.</t>
+  </si>
+  <si>
+    <t>Dwarf Lanternshark</t>
+  </si>
+  <si>
+    <t>Etmopterus perryi</t>
+  </si>
+  <si>
+    <t>[FreePlayFishFromHand][Bioluminescent] only</t>
+  </si>
+  <si>
+    <t>One of the smallest known sharks, the dwarf lanternshark's bioluminescent belly helps it blend in with sunlight from above.</t>
+  </si>
+  <si>
+    <t>Epaulette Shark</t>
+  </si>
+  <si>
+    <t>Hemiscyllium ocellatum</t>
+  </si>
+  <si>
+    <t>[BlueCoral][UnSchoolFish]</t>
+  </si>
+  <si>
+    <t>It can swim, but it mostly “walks” along coral reefs on its fins. It can even travel short distances over land.</t>
+  </si>
+  <si>
+    <t>Filetail Catshark</t>
+  </si>
+  <si>
+    <t>Parmaturus xaniurus</t>
+  </si>
+  <si>
+    <t>[FishFromHandConsume]</t>
+  </si>
+  <si>
+    <t>This catshark's common name comes from the toothlike projections on its skin.</t>
+  </si>
+  <si>
+    <t>Fire Dartfish</t>
+  </si>
+  <si>
+    <t>Nemateleotris magnifica</t>
+  </si>
+  <si>
+    <t>[PurpleCoral][PurpleCoral][PurpleCoral]</t>
+  </si>
+  <si>
+    <t>It usually hovers above its burrow, quick to dart inside. It flicks its long dorsal fin back and forth, perhaps as a signal.</t>
+  </si>
+  <si>
     <t>any:1</t>
-  </si>
-  <si>
-    <t>Common Bluestripe Snapper</t>
-  </si>
-  <si>
-    <t>Lutjanus kasmira</t>
-  </si>
-  <si>
-    <t>[BlueCoral][BlueCoral][BlueCoral]</t>
-  </si>
-  <si>
-    <t>It has a varied diet, feeding on fishes, shrimps, crabs, and crustaceans, as well as plant and algae material.</t>
-  </si>
-  <si>
-    <t>Daggertooth</t>
-  </si>
-  <si>
-    <t>Anotopterus pharao</t>
-  </si>
-  <si>
-    <t>[FishHatch] also, if [GreenCoral][GreenCoral][GreenCoral] in this dive site: [Discard]</t>
-  </si>
-  <si>
-    <t>Older daggertooth appear to turn black, lose their teeth, and migrate to deeper waters, possibly to reproduce.</t>
-  </si>
-  <si>
-    <t>Dusky Shark</t>
-  </si>
-  <si>
-    <t>Carcharhinus obscurus</t>
-  </si>
-  <si>
-    <t>[FreePlayFishFromHand][FishLengthMedium]only</t>
-  </si>
-  <si>
-    <t>It migrates hundreds to thousands of km to temperate waters in the summer and toward the equator in the winter.</t>
-  </si>
-  <si>
-    <t>Dwarf Lanternshark</t>
-  </si>
-  <si>
-    <t>Etmopterus perryi</t>
-  </si>
-  <si>
-    <t>[FreePlayFishFromHand][Bioluminescent] only</t>
-  </si>
-  <si>
-    <t>One of the smallest known sharks, the dwarf lanternshark's bioluminescent belly helps it blend in with sunlight from above.</t>
-  </si>
-  <si>
-    <t>Epaulette Shark</t>
-  </si>
-  <si>
-    <t>Hemiscyllium ocellatum</t>
-  </si>
-  <si>
-    <t>[BlueCoral][UnSchoolFish]</t>
-  </si>
-  <si>
-    <t>It can swim, but it mostly “walks” along coral reefs on its fins. It can even travel short distances over land.</t>
-  </si>
-  <si>
-    <t>Filetail Catshark</t>
-  </si>
-  <si>
-    <t>Parmaturus xaniurus</t>
-  </si>
-  <si>
-    <t>[FishFromHandConsume]</t>
-  </si>
-  <si>
-    <t>This catshark's common name comes from the toothlike projections on its skin.</t>
-  </si>
-  <si>
-    <t>Fire Dartfish</t>
-  </si>
-  <si>
-    <t>Nemateleotris magnifica</t>
-  </si>
-  <si>
-    <t>[PurpleCoral][PurpleCoral][PurpleCoral]</t>
-  </si>
-  <si>
-    <t>It usually hovers above its burrow, quick to dart inside. It flicks its long dorsal fin back and forth, perhaps as a signal.</t>
   </si>
   <si>
     <t>Flame Angelfish</t>
@@ -11101,9 +11101,7 @@
       <c r="U146" s="2">
         <v>0.0</v>
       </c>
-      <c r="V146" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="V146" s="2"/>
       <c r="W146" s="2" t="s">
         <v>558</v>
       </c>
@@ -11185,9 +11183,7 @@
       <c r="X147" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="Y147" s="2" t="s">
-        <v>563</v>
-      </c>
+      <c r="Y147" s="2"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="2">
@@ -11197,10 +11193,10 @@
         <v>25</v>
       </c>
       <c r="C148" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D148" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="E148" s="2">
         <v>1.0</v>
@@ -11236,7 +11232,7 @@
         <v>28</v>
       </c>
       <c r="P148" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="Q148" s="2">
         <v>0.0</v>
@@ -11257,7 +11253,7 @@
         <v>78</v>
       </c>
       <c r="W148" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="X148" s="2" t="s">
         <v>522</v>
@@ -11272,10 +11268,10 @@
         <v>25</v>
       </c>
       <c r="C149" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D149" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>569</v>
       </c>
       <c r="E149" s="2">
         <v>0.0</v>
@@ -11311,7 +11307,7 @@
         <v>47</v>
       </c>
       <c r="P149" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="Q149" s="2">
         <v>0.0</v>
@@ -11332,7 +11328,7 @@
         <v>83</v>
       </c>
       <c r="W149" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X149" s="2" t="s">
         <v>522</v>
@@ -11347,10 +11343,10 @@
         <v>25</v>
       </c>
       <c r="C150" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D150" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="E150" s="2">
         <v>0.0</v>
@@ -11386,7 +11382,7 @@
         <v>28</v>
       </c>
       <c r="P150" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="Q150" s="2">
         <v>0.0</v>
@@ -11405,7 +11401,7 @@
       </c>
       <c r="V150" s="2"/>
       <c r="W150" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="X150" s="2" t="s">
         <v>522</v>
@@ -11420,10 +11416,10 @@
         <v>25</v>
       </c>
       <c r="C151" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D151" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="E151" s="2">
         <v>2.0</v>
@@ -11459,7 +11455,7 @@
         <v>34</v>
       </c>
       <c r="P151" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="Q151" s="2">
         <v>1.0</v>
@@ -11478,7 +11474,7 @@
       </c>
       <c r="V151" s="2"/>
       <c r="W151" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="X151" s="2" t="s">
         <v>522</v>
@@ -11493,10 +11489,10 @@
         <v>25</v>
       </c>
       <c r="C152" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D152" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>581</v>
       </c>
       <c r="E152" s="2">
         <v>0.0</v>
@@ -11532,28 +11528,26 @@
         <v>34</v>
       </c>
       <c r="P152" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q152" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="R152" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="S152" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="T152" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="U152" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="V152" s="2"/>
+      <c r="W152" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="Q152" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="R152" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="S152" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="T152" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="U152" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="V152" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="W152" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="X152" s="2" t="s">
         <v>522</v>
@@ -11570,10 +11564,10 @@
         <v>25</v>
       </c>
       <c r="C153" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D153" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="E153" s="2">
         <v>3.0</v>
@@ -11609,7 +11603,7 @@
         <v>47</v>
       </c>
       <c r="P153" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="Q153" s="2">
         <v>0.0</v>
@@ -11628,7 +11622,7 @@
       </c>
       <c r="V153" s="2"/>
       <c r="W153" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="X153" s="2" t="s">
         <v>522</v>
@@ -11643,10 +11637,10 @@
         <v>25</v>
       </c>
       <c r="C154" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D154" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="E154" s="2">
         <v>0.0</v>
@@ -11682,34 +11676,32 @@
         <v>28</v>
       </c>
       <c r="P154" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="Q154" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="R154" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="S154" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="T154" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="U154" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="V154" s="2"/>
+      <c r="W154" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="Q154" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="R154" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="S154" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="T154" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="U154" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="V154" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="W154" s="2" t="s">
-        <v>591</v>
       </c>
       <c r="X154" s="2" t="s">
         <v>522</v>
       </c>
       <c r="Y154" s="2" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
@@ -11776,7 +11768,9 @@
       <c r="U155" s="2">
         <v>0.0</v>
       </c>
-      <c r="V155" s="2"/>
+      <c r="V155" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="W155" s="2" t="s">
         <v>595</v>
       </c>
@@ -11851,7 +11845,9 @@
       <c r="U156" s="2">
         <v>1.0</v>
       </c>
-      <c r="V156" s="2"/>
+      <c r="V156" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="W156" s="2" t="s">
         <v>599</v>
       </c>
@@ -12445,9 +12441,7 @@
       <c r="U164" s="2">
         <v>0.0</v>
       </c>
-      <c r="V164" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="V164" s="2"/>
       <c r="W164" s="2" t="s">
         <v>632</v>
       </c>
@@ -13276,7 +13270,7 @@
         <v>522</v>
       </c>
       <c r="Y175" s="2" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
@@ -13493,9 +13487,7 @@
       <c r="U178" s="2">
         <v>0.0</v>
       </c>
-      <c r="V178" s="2" t="s">
-        <v>78</v>
-      </c>
+      <c r="V178" s="2"/>
       <c r="W178" s="2" t="s">
         <v>687</v>
       </c>
@@ -13801,7 +13793,7 @@
         <v>522</v>
       </c>
       <c r="Y182" s="2" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
@@ -13876,7 +13868,7 @@
         <v>522</v>
       </c>
       <c r="Y183" s="2" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
     </row>
     <row r="184" ht="15.75" customHeight="1">
@@ -15293,7 +15285,9 @@
       <c r="U202" s="2">
         <v>0.0</v>
       </c>
-      <c r="V202" s="2"/>
+      <c r="V202" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="W202" s="2" t="s">
         <v>777</v>
       </c>
@@ -15676,7 +15670,7 @@
         <v>522</v>
       </c>
       <c r="Y207" s="2" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1">
@@ -15824,7 +15818,7 @@
         <v>522</v>
       </c>
       <c r="Y209" s="2" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">

--- a/scripts/cards.xlsx
+++ b/scripts/cards.xlsx
@@ -361,7 +361,7 @@
     <t>Black Swallower</t>
   </si>
   <si>
-    <t>Chiasmodor niger</t>
+    <t>Chiasmodon niger</t>
   </si>
   <si>
     <t>[FishFromHand][ArrowDown][FlipperGreen]</t>
@@ -547,7 +547,7 @@
     <t>Elsman's Whipnose</t>
   </si>
   <si>
-    <t>Gigantactic elsmani</t>
+    <t>Gigantactis elsmani</t>
   </si>
   <si>
     <t>[DrawCard][Discard][SchoolFeederMove]</t>
@@ -580,7 +580,7 @@
     <t>European Anchovy</t>
   </si>
   <si>
-    <t>Endraulis encrasicolus</t>
+    <t>Engraulis encrasicolus</t>
   </si>
   <si>
     <t>[FishEgg][ArrowDown][Estuary]</t>
@@ -652,7 +652,7 @@
     <t>Footballfish</t>
   </si>
   <si>
-    <t>Himantolophus naucifilosus</t>
+    <t>Himantolophus paucifilosus</t>
   </si>
   <si>
     <t>The modified ray on its head makes a thick fishing rod, tipped with a luminous bulb, used to lure prey.</t>
@@ -661,7 +661,7 @@
     <t>Giant Devil Ray</t>
   </si>
   <si>
-    <t>Mohula mohular</t>
+    <t>Mobula mobular</t>
   </si>
   <si>
     <t>[YoungFish][YoungFish]</t>
@@ -697,7 +697,7 @@
     <t>Giant Manta Ray</t>
   </si>
   <si>
-    <t>Mohula birostris</t>
+    <t>Mobula birostris</t>
   </si>
   <si>
     <t>[YoungFish][YoungFish][YoungFish]</t>
@@ -856,7 +856,7 @@
     <t>Japanese Anchovy</t>
   </si>
   <si>
-    <t>Endraulis japonicus</t>
+    <t>Engraulis japonicus</t>
   </si>
   <si>
     <t>Large schools tend to swim close to the surface during the full moon, their silver scales shimmering in the light.</t>
@@ -961,7 +961,7 @@
     <t>Its common name means “strong-strong” in Hawaiian. Flyingfishes make up nearly 25% of the diet of adults.</t>
   </si>
   <si>
-    <t>Maletese Ray</t>
+    <t>Maltese Ray</t>
   </si>
   <si>
     <t>Leucoraja melitensis</t>
@@ -1006,7 +1006,7 @@
     <t>This fish has often been seen suspending itself vertically in the water, with its mouth pointing up towards the surface.</t>
   </si>
   <si>
-    <t>Ocean sunfish</t>
+    <t>Ocean Sunfish</t>
   </si>
   <si>
     <t>Mola mola</t>
@@ -1429,7 +1429,7 @@
     <t>Whitemargin Stargazer</t>
   </si>
   <si>
-    <t>Uranoschopus sulphureus</t>
+    <t>Uranoscopus sulphureus</t>
   </si>
   <si>
     <t>This venomous fish has electric organs located in a pouch behind its eyes and can discharge up to 50 volts.</t>
@@ -1456,7 +1456,7 @@
     <t>Yellowtail Snapper</t>
   </si>
   <si>
-    <t>Ocyurum chrysurus</t>
+    <t>Ocyurus chrysurus</t>
   </si>
   <si>
     <t>Its Latin name is derived from the words “golden swift tail” because its bright yellow tail is forked like that of a swift.</t>
@@ -1498,7 +1498,7 @@
     <t>Smoothcheek Lanternfish</t>
   </si>
   <si>
-    <t>Bolinichtys indicus</t>
+    <t>Bolinichthys indicus</t>
   </si>
   <si>
     <t>[FishEgg][FishEgg][DrawCard][DrawCard]</t>
@@ -2549,12 +2549,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -2853,7 +2856,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="8.86"/>
+    <col customWidth="1" min="1" max="2" width="8.86"/>
+    <col customWidth="1" min="3" max="3" width="26.14"/>
+    <col customWidth="1" min="4" max="4" width="27.43"/>
     <col customWidth="1" min="5" max="5" width="9.14"/>
     <col customWidth="1" min="6" max="6" width="8.86"/>
     <col customWidth="1" min="7" max="7" width="10.43"/>
@@ -2862,15 +2867,15 @@
     <col customWidth="1" min="10" max="11" width="8.86"/>
     <col customWidth="1" min="12" max="12" width="9.29"/>
     <col customWidth="1" min="13" max="14" width="8.86"/>
-    <col customWidth="1" min="15" max="15" width="10.86"/>
-    <col customWidth="1" min="16" max="16" width="8.86"/>
+    <col customWidth="1" min="15" max="15" width="11.86"/>
+    <col customWidth="1" min="16" max="16" width="95.43"/>
     <col customWidth="1" min="17" max="17" width="14.43"/>
     <col customWidth="1" min="18" max="18" width="11.43"/>
     <col customWidth="1" min="19" max="19" width="8.86"/>
     <col customWidth="1" min="20" max="20" width="9.14"/>
     <col customWidth="1" min="21" max="21" width="10.86"/>
     <col customWidth="1" min="22" max="22" width="8.86"/>
-    <col customWidth="1" min="23" max="23" width="11.14"/>
+    <col customWidth="1" min="23" max="23" width="116.14"/>
     <col customWidth="1" min="24" max="24" width="10.29"/>
     <col customWidth="1" min="25" max="25" width="9.43"/>
     <col customWidth="1" min="26" max="26" width="8.86"/>
@@ -4120,7 +4125,7 @@
       <c r="C23" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>116</v>
       </c>
       <c r="E23" s="2"/>
@@ -4748,7 +4753,9 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
+      <c r="U34" s="3">
+        <v>1.0</v>
+      </c>
       <c r="V34" s="2"/>
       <c r="W34" s="2" t="s">
         <v>160</v>
@@ -4914,7 +4921,9 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
-      <c r="T37" s="2"/>
+      <c r="T37" s="3">
+        <v>2.0</v>
+      </c>
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2" t="s">
@@ -4990,7 +4999,7 @@
       <c r="C39" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="3" t="s">
         <v>178</v>
       </c>
       <c r="E39" s="2"/>
@@ -5157,7 +5166,7 @@
       <c r="C42" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="3" t="s">
         <v>189</v>
       </c>
       <c r="E42" s="2">
@@ -5534,7 +5543,7 @@
       <c r="C49" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="3" t="s">
         <v>213</v>
       </c>
       <c r="E49" s="2">
@@ -5593,7 +5602,7 @@
       <c r="C50" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="3" t="s">
         <v>216</v>
       </c>
       <c r="E50" s="2">
@@ -5760,7 +5769,7 @@
       <c r="C53" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="3" t="s">
         <v>228</v>
       </c>
       <c r="E53" s="2">
@@ -6538,7 +6547,7 @@
       <c r="C67" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="3" t="s">
         <v>281</v>
       </c>
       <c r="E67" s="2">
@@ -7077,7 +7086,7 @@
       <c r="B77" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="4" t="s">
         <v>316</v>
       </c>
       <c r="D77" s="2" t="s">
@@ -7348,7 +7357,7 @@
       <c r="B82" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="3" t="s">
         <v>331</v>
       </c>
       <c r="D82" s="2" t="s">
@@ -9632,7 +9641,7 @@
       <c r="C123" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D123" s="3" t="s">
         <v>472</v>
       </c>
       <c r="E123" s="2">
@@ -9801,7 +9810,7 @@
       <c r="C126" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D126" s="3" t="s">
         <v>481</v>
       </c>
       <c r="E126" s="2">
@@ -10011,7 +10020,7 @@
       <c r="C130" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="D130" s="3" t="s">
         <v>495</v>
       </c>
       <c r="E130" s="2">

--- a/scripts/cards.xlsx
+++ b/scripts/cards.xlsx
@@ -1861,8 +1861,7 @@
     <t>(all players) [PurpleCoral][PurpleCoral] [AllPlayers]</t>
   </si>
   <si>
-    <t>Sheltering by day in crevices up to  -50 meters deep, this nocturnal ambush predator hunts primarily by smell.</t>
+    <t>Sheltering by day in crevices up to 50 meters deep, this nocturnal ambush predator hunts primarily by smell.</t>
   </si>
   <si>
     <t>Goblin Shark</t>
@@ -12155,7 +12154,7 @@
         <v>0.0</v>
       </c>
       <c r="V160" s="2"/>
-      <c r="W160" s="2" t="s">
+      <c r="W160" s="3" t="s">
         <v>616</v>
       </c>
       <c r="X160" s="2" t="s">

--- a/scripts/cards.xlsx
+++ b/scripts/cards.xlsx
@@ -9114,7 +9114,9 @@
       <c r="S113" s="2"/>
       <c r="T113" s="2"/>
       <c r="U113" s="2"/>
-      <c r="V113" s="2"/>
+      <c r="V113" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="W113" s="2" t="s">
         <v>440</v>
       </c>
@@ -11257,9 +11259,7 @@
       <c r="U148" s="2">
         <v>0.0</v>
       </c>
-      <c r="V148" s="2" t="s">
-        <v>78</v>
-      </c>
+      <c r="V148" s="2"/>
       <c r="W148" s="2" t="s">
         <v>566</v>
       </c>
@@ -15068,7 +15068,7 @@
       <c r="U199" s="2">
         <v>0.0</v>
       </c>
-      <c r="V199" s="2" t="s">
+      <c r="V199" s="3" t="s">
         <v>65</v>
       </c>
       <c r="W199" s="2" t="s">
